--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -11,11 +11,16 @@
     <sheet name="BOM" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">Reference</t>
   </si>
@@ -125,22 +130,52 @@
     <t xml:space="preserve">HLK-PM01 115VAC to 5VDC power supply</t>
   </si>
   <si>
+    <t xml:space="preserve">Display</t>
+  </si>
+  <si>
     <t xml:space="preserve">Freenove LCD 1602 display</t>
   </si>
   <si>
+    <t xml:space="preserve">Current sensor</t>
+  </si>
+  <si>
     <t xml:space="preserve">Amploc AMP25 current sensor</t>
   </si>
   <si>
+    <t xml:space="preserve">Transformer</t>
+  </si>
+  <si>
     <t xml:space="preserve">Transformer, 13.6 VAC</t>
   </si>
   <si>
-    <t xml:space="preserve">microUSB extender</t>
+    <t xml:space="preserve">Cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">microUSB extender, e.g Poyiccot Micro USB Extension Cable, 90 Degree Right Angle Micro USB Male to Micro USB Female Power Extension Panel Mount Type Cable for Data &amp; Charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output socket</t>
   </si>
   <si>
     <t xml:space="preserve">female AC socket</t>
   </si>
   <si>
+    <t xml:space="preserve">Input socket</t>
+  </si>
+  <si>
     <t xml:space="preserve">male AC power socket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Box </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junction Box, Zulkit Project Box IP65 Waterproof Outdoor Box ABS Plastic Electrical Boxes Electronic Enclosure Black 7.9 x 4.7 x 2.95 inch (200 x 120 x 75mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bezel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3D printed per stp file</t>
   </si>
 </sst>
 </file>
@@ -150,11 +185,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -170,6 +206,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -214,9 +257,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -342,189 +405,223 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="37.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="61.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="4.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="37.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="61.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="4.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5.32"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="B19" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
-        <v>37</v>
+      <c r="A20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="s">
-        <v>39</v>
+      <c r="A21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="54.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="s">
-        <v>40</v>
+      <c r="A23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
-        <v>41</v>
+      <c r="A24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
